--- a/data/trans_orig/IP05A07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP05A07-Clase-trans_orig.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32487</t>
+          <t>31288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40921</t>
+          <t>40394</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56672</t>
+          <t>55882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76668</t>
+          <t>78172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>99996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,65%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>26653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41649</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>22330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51830</t>
+          <t>51589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72780</t>
+          <t>73097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23607</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22585</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39432</t>
+          <t>39514</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>40915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56591</t>
+          <t>57767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36982</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52480</t>
+          <t>52472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82779</t>
+          <t>83713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105768</t>
+          <t>104927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,21%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27050</t>
+          <t>27437</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42365</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46615</t>
+          <t>45783</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61604</t>
+          <t>62253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83519</t>
+          <t>83485</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14064</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>20490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31118</t>
+          <t>32201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38059</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46370</t>
+          <t>45791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60939</t>
+          <t>60655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88301</t>
+          <t>87607</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109592</t>
+          <t>109219</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36762</t>
+          <t>37233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45060</t>
+          <t>45352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65187</t>
+          <t>65442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99420</t>
+          <t>99364</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123084</t>
+          <t>122181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106857</t>
+          <t>107020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131741</t>
+          <t>131636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211613</t>
+          <t>210048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>246188</t>
+          <t>244498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,49%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59261</t>
+          <t>60561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82052</t>
+          <t>81781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67031</t>
+          <t>67251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90516</t>
+          <t>91336</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133423</t>
+          <t>135272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>168201</t>
+          <t>167815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>16889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32093</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39651</t>
+          <t>39155</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42799</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66453</t>
+          <t>64971</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80130</t>
+          <t>79960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99415</t>
+          <t>100130</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72424</t>
+          <t>72660</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92894</t>
+          <t>92132</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158624</t>
+          <t>158043</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>185532</t>
+          <t>186993</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35220</t>
+          <t>33893</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53499</t>
+          <t>51926</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30592</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48833</t>
+          <t>49149</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71054</t>
+          <t>70754</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>95393</t>
+          <t>97578</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23883</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27391</t>
+          <t>26179</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25911</t>
+          <t>26408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44306</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19828</t>
+          <t>20179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32021</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21421</t>
+          <t>21988</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>35603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>45624</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>63341</t>
+          <t>63746</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27668</t>
+          <t>27242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>30386</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45607</t>
+          <t>45327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50279</t>
+          <t>50123</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68360</t>
+          <t>68252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11413</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>338456</t>
+          <t>339002</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>381816</t>
+          <t>382346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>353680</t>
+          <t>353276</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>399484</t>
+          <t>396830</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>703746</t>
+          <t>707198</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>767531</t>
+          <t>767753</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>214148</t>
+          <t>214716</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>254470</t>
+          <t>256147</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>228325</t>
+          <t>228502</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>269796</t>
+          <t>269883</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>454748</t>
+          <t>454561</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>514042</t>
+          <t>510854</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70101</t>
+          <t>69766</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>99429</t>
+          <t>98367</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>76641</t>
+          <t>77486</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>106633</t>
+          <t>107648</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>154601</t>
+          <t>156094</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>194832</t>
+          <t>199149</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52793</t>
+          <t>53275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66376</t>
+          <t>66898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60091</t>
+          <t>58677</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74572</t>
+          <t>74752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117232</t>
+          <t>117040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137779</t>
+          <t>137898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18685</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30433</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27916</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45222</t>
+          <t>44864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>15575</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53426</t>
+          <t>53883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69997</t>
+          <t>70113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67383</t>
+          <t>67538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82961</t>
+          <t>83710</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126383</t>
+          <t>125824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149094</t>
+          <t>148657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24059</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38844</t>
+          <t>39518</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36286</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49289</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>72749</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>18903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>28397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31253</t>
+          <t>31913</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43517</t>
+          <t>44392</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53633</t>
+          <t>53678</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76180</t>
+          <t>74750</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>94047</t>
+          <t>92912</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24984</t>
+          <t>24783</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28108</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47882</t>
+          <t>49787</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19408</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136545</t>
+          <t>138444</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160379</t>
+          <t>160347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132862</t>
+          <t>132963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155677</t>
+          <t>154537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>274987</t>
+          <t>277693</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>307995</t>
+          <t>309135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45566</t>
+          <t>44900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67165</t>
+          <t>65592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>31524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51169</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81937</t>
+          <t>81507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111693</t>
+          <t>109238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26846</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>35196</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36027</t>
+          <t>35125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58314</t>
+          <t>56531</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78673</t>
+          <t>79812</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96104</t>
+          <t>97218</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83105</t>
+          <t>84059</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101850</t>
+          <t>102676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168579</t>
+          <t>167515</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196073</t>
+          <t>193399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30158</t>
+          <t>29933</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47250</t>
+          <t>46337</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24221</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>40236</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>56439</t>
+          <t>58111</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>81840</t>
+          <t>81733</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25667</t>
+          <t>26692</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19971</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36516</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31419</t>
+          <t>30896</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43724</t>
+          <t>42881</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33466</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47010</t>
+          <t>46882</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>68096</t>
+          <t>68719</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>87396</t>
+          <t>86658</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22680</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28206</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>30430</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>413824</t>
+          <t>415329</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>454124</t>
+          <t>453211</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>447354</t>
+          <t>448715</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>487663</t>
+          <t>489433</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>873567</t>
+          <t>874623</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>929900</t>
+          <t>931822</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>155463</t>
+          <t>154644</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>193408</t>
+          <t>190989</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147994</t>
+          <t>147328</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>185166</t>
+          <t>183852</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>312984</t>
+          <t>312099</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>366291</t>
+          <t>364132</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>49982</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>73718</t>
+          <t>73775</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62238</t>
+          <t>62477</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>88828</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>119558</t>
+          <t>119580</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>155917</t>
+          <t>155887</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69786</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84919</t>
+          <t>85773</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92643</t>
+          <t>92814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113317</t>
+          <t>113286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167331</t>
+          <t>169150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193639</t>
+          <t>193601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>21032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35539</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>27274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50183</t>
+          <t>49517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14467</t>
+          <t>14628</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>28649</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59256</t>
+          <t>58752</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73992</t>
+          <t>73598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62757</t>
+          <t>61809</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>77570</t>
+          <t>77626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126345</t>
+          <t>125951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146420</t>
+          <t>146351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21173</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40094</t>
+          <t>40876</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30710</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28683</t>
+          <t>28716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40080</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48353</t>
+          <t>49500</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59060</t>
+          <t>59212</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>81126</t>
+          <t>81599</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>97004</t>
+          <t>96943</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16696</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25067</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101472</t>
+          <t>100034</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177778</t>
+          <t>178498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>147012</t>
+          <t>146658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>174161</t>
+          <t>173835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236776</t>
+          <t>252583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>341277</t>
+          <t>342626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>25530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107037</t>
+          <t>108687</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46632</t>
+          <t>43530</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>54474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164445</t>
+          <t>159252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36723</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27957</t>
+          <t>26753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52439</t>
+          <t>50485</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>79117</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95846</t>
+          <t>95997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>119104</t>
+          <t>118524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>139039</t>
+          <t>139482</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204869</t>
+          <t>205369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>231983</t>
+          <t>231566</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29317</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50995</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>17699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16751</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33174</t>
+          <t>33316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>54348</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63974</t>
+          <t>64242</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44506</t>
+          <t>44825</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58720</t>
+          <t>58456</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>104032</t>
+          <t>104193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>120745</t>
+          <t>120591</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>20188</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27548</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>406508</t>
+          <t>415412</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>510071</t>
+          <t>512435</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>552011</t>
+          <t>548285</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>596529</t>
+          <t>595686</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>981693</t>
+          <t>976670</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1091899</t>
+          <t>1090591</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,62%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>91163</t>
+          <t>90254</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>204480</t>
+          <t>196650</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88666</t>
+          <t>89661</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125407</t>
+          <t>129602</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>191869</t>
+          <t>192970</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>312057</t>
+          <t>326004</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41834</t>
+          <t>42935</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>68742</t>
+          <t>68222</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54215</t>
+          <t>54720</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>85739</t>
+          <t>85460</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>103067</t>
+          <t>104889</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>142578</t>
+          <t>143485</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
